--- a/cosmos-bc-dss/reports/COSMoS_BC_DSS_QC.xlsx
+++ b/cosmos-bc-dss/reports/COSMoS_BC_DSS_QC.xlsx
@@ -586,7 +586,7 @@
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08</t>
+          <t>Generated: 2026-03-10</t>
         </is>
       </c>
     </row>

--- a/cosmos-bc-dss/reports/COSMoS_BC_DSS_QC.xlsx
+++ b/cosmos-bc-dss/reports/COSMoS_BC_DSS_QC.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QC_Report" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'QC_Report'!$A$1:$E$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'QC_Report'!$A$1:$E$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -756,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1160,8 +1160,33 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>QC-14</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>TESTCD_NCIt differs from NCIt_Code</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>HEIGHT (Body Height): BC=C164634 TESTCD=C25347 | WEIGHT (Body Weight): BC=C81328 TESTCD=C25208 | INTP (Electrocardiogram Analysis): BC=C181655 TESTCD=C41255 | GLUCPE (Glucose Measurement): BC=C105585 TESTCD=C163446 | MICROCY (Microcyte to Erythrocyte Ratio): BC=C201227 TESTCD=C64822 | LENGTH (Organ Craniocaudal Length Meas): BC=C135509 TESTCD=C25334 | HCG (Serum HCG Measurement): BC=C73495 TESTCD=C64851</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E16"/>
+  <autoFilter ref="A1:E17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cosmos-bc-dss/reports/COSMoS_BC_DSS_QC.xlsx
+++ b/cosmos-bc-dss/reports/COSMoS_BC_DSS_QC.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QC_Report" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'QC_Report'!$A$1:$E$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'QC_Report'!$A$1:$E$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -756,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1185,8 +1185,33 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>QC-15</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>BC_Scope=Study: trial-level metadata included as BCs</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>193</v>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>192 BCs, 129 DSS rows, 63 hierarchy rows | Domains: TS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E17"/>
+  <autoFilter ref="A1:E18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cosmos-bc-dss/reports/COSMoS_BC_DSS_QC.xlsx
+++ b/cosmos-bc-dss/reports/COSMoS_BC_DSS_QC.xlsx
@@ -30,10 +30,10 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
@@ -94,19 +94,13 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -126,42 +120,39 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -538,208 +529,208 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SECTION</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ITEM</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr"/>
-      <c r="B2" s="3" t="inlineStr"/>
-      <c r="C2" s="3" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>PURPOSE</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr"/>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>QC report for COSMoS_BC_DSS_Flatten output</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr"/>
-      <c r="B4" s="3" t="inlineStr"/>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Validates interim/COSMoS_BC_DSS.xlsx against structural and curation-principle checks</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr"/>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Generated: 2026-03-10</t>
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Generated: 2026-04-09</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr"/>
-      <c r="B6" s="3" t="inlineStr"/>
-      <c r="C6" s="3" t="inlineStr"/>
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>SHEETS</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr"/>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>README</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>This sheet</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr"/>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>QC_Report</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>All QC check results with severity, count, and detail</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr"/>
-      <c r="B10" s="3" t="inlineStr"/>
-      <c r="C10" s="3" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>CHECK TYPES</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr"/>
-      <c r="C11" s="4" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>QC-01 to QC-10</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Structural pipeline checks</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr"/>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>QC-11 to QC-13</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Validated against CDISC BC Curation Principles and Completion Guidelines</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr"/>
-      <c r="B14" s="3" t="inlineStr"/>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>(COSMoS bc_starter_package -- BC Curation Principles and Completion GLs.xlsx)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr"/>
-      <c r="B15" s="3" t="inlineStr"/>
-      <c r="C15" s="3" t="inlineStr"/>
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>SEVERITY</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr"/>
-      <c r="C16" s="4" t="inlineStr"/>
+      <c r="B16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr"/>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Structural integrity failure -- investigate before using output</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr"/>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Potential issue -- review recommended, may be expected for some COSMoS versions</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr"/>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Informational -- documents expected patterns or gap analysis</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr"/>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Check passed, no issues found</t>
         </is>
@@ -767,444 +758,444 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>QC-01</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>CT unmapped: Specimen</t>
         </is>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>C113243 (2 usages) | C449 (26 usages) | C812 (7 usages) | C95940 (3 usages)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>QC-02</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>CT unmapped: Method</t>
         </is>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="D3" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>AUTOPSY (1 usages) | C179788 (1 usages) | PINCH DYNAMOMETRY (1 usages)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>QC-03</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>CT unmapped: Unit</t>
         </is>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="9" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>QC-04</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>DSS rows with no TESTCD (no CT test code in COSMoS source)</t>
         </is>
       </c>
-      <c r="D5" s="11" t="n">
-        <v>46</v>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="D5" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>ADVEVENT (DS) | ARIGEABCH (IS) | ARIGEABFP (IS) | ARIGEABM (IS) | ARIGEABMR (IS) | ARIGEABPC (IS) | BRTHDTC (DM) | PROTCOMP (DS) | CTSCAN (PR) | CTSCANCHEST (PR)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>QC-05</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Specimen present but Specimen_NCIt blank</t>
         </is>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>C449 | C812 | C113243 | C95940</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>QC-06</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Quantitative DS rows with no Allowed_Units</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n">
-        <v>106</v>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>DM: 1 | FT: 16 | GF: 11 | LB: 4 | MI: 7 | MK: 25 | QS: 1 | RP: 27 | RS: 3 | SR: 1 | TS: 8 | UR: 2</t>
+      <c r="D7" s="6" t="n">
+        <v>133</v>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>DM: 1 | FT: 16 | GF: 11 | LB: 4 | MI: 7 | MK: 25 | QS: 1 | RE: 15 | RP: 27 | RS: 3 | SR: 1 | TS: 8 | UR: 2 | VS: 12</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>QC-07</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>GLUCSERPL specimen is SERUM -- expected SERUM OR PLASMA per *SERPL pattern</t>
         </is>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>GLUCSERPL Specimen='SERUM' | Recommend reporting to CDISC COSMoS curators for correction at source</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>QC-08</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Multi-result DSS (same TESTCD+Domain+Specimen)</t>
         </is>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>IS ARIGEAB (SERUM; SERUM OR PLASMA; BLOOD) x87 | IS MBIGGAB (SERUM; SERUM OR PLASMA; BLOOD) x63 | IS ARIGGAB (SERUM; SERUM OR PLASMA; BLOOD) x53 | IS MBIMAB (SERUM; SERUM OR PLASMA; BLOOD) x52 | IS ARIGAAB (SERUM; SERUM OR PLASMA; BLOOD) x17 | IS ATIGMAB (SERUM; SERUM OR PLASMA; BLOOD) x12 | GF SEQREAR (C449) x6 | GF SNV (C449) x6 | GF SHRTVAR (C449) x5 | GF TRNSCPTN (C812) x5</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>QC-09</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>BC_only_no_DS (194 BCs) -- top categories</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>194</v>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>BC_only_no_DS (192 BCs) -- top categories</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>192</v>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>QRS: 119 | Functional Assessment: 96 | ADAS-Cog: 95 | ADC: 95 | Alzheimer's Disease Assessment Scale-Cognitive CDISC Version Functional Test: 95 | ADAS-Cog CDISC Version Functional Test Question: 94 | Laboratory Tests: 16 | Clinical or Research Assessment Classification: 14 | Gene Expression Analysis: 11 | Genetic Testing: 10</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>QC-10</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>WARNING</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Retired BCs included in output</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Adverse Event [RETIRED] | Anticipated Adverse Event [RETIRED] | Complete [RETIRED] | Dead [RETIRED] | Failure To Meet Continuation Criteria [RETIRED] | Failure to Meet Randomization Criteria [RETIRED] | Lack of Efficacy [RETIRED] | Lost To Follow-Up [RETIRED] | Medical History Reported Term [RETIRED] | Physician Decision [RETIRED]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>QC-11a</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Result_Scale='Qualitative' -- COSMoS source term, not in curation principles valid set</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>502</v>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>DD: 12 | EG: 33 | FA: 12 | GF: 22 | IE: 2 | IS: 138 | LB: 28 | MB: 7 | MK: 4 | QS: 16 | RE: 10 | RP: 55 | RS: 132 | SC: 1 | SR: 6 | TR: 7 | TU: 10 | UR: 5 | VS: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>QC-11b</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Result_Scale='datetime' -- likely maps to Temporal per curation principles</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>RP: 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>QC-11c</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Result_Scale: no unexpected values</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>QC-12</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Placeholder BC_IDs (NCIt code pending)</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>NEW_LZZT (TTS Acceptability Survey) | NEW_LZZT4 (TTS Acceptability Survey -  Pa) | NEW_LZZT1 (TTS Acceptability Survey -  Pa) | NEW_LZZT3 (TTS Acceptability Survey -  Pa) | NEW_LZZT2 (TTS Acceptability Survey -  Pa) | NEW_1 (Urine Glucose Test Strip Measu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>QC-13</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>BC_Synonyms: preferred term not stripped</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Anticipated Adverse Event [RETIRED] | Medical History Reported Term [RETIRED] | Reported Event Term [RETIRED] | Urine Glucose Test Strip Measurement [RETIRED]</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>QC-11a</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Result_Scale='Qualitative' -- COSMoS source term, not in curation principles valid set</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>491</v>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>DD: 12 | EG: 33 | FA: 12 | GF: 22 | IE: 2 | IS: 138 | LB: 28 | MB: 7 | MK: 4 | QS: 16 | RP: 55 | RS: 132 | SC: 1 | SR: 6 | TR: 7 | TU: 10 | UR: 5 | VS: 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>QC-11b</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Result_Scale='datetime' -- likely maps to Temporal per curation principles</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="n">
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>C100106 (ADAS-Cog CDISC Version Functio) | C211913 (CDISC QRS Instruments Question) | C91102 (Clinical or Research Assessmen) | C101875 (EQ-5D-5L Questionnaire Questio)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>QC-14</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>TESTCD_NCIt differs from NCIt_Code</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>RP: 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>QC-11c</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Result_Scale: no unexpected values</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="9" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>QC-12</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>HEIGHT (Body Height): BC=C164634 TESTCD=C25347 | WEIGHT (Body Weight): BC=C81328 TESTCD=C25208 | INTP (Electrocardiogram Analysis): BC=C181655 TESTCD=C41255 | GLUCPE (Glucose Measurement): BC=C105585 TESTCD=C163446 | MICROCY (Microcyte to Erythrocyte Ratio): BC=C201227 TESTCD=C64822 | LENGTH (Organ Craniocaudal Length Meas): BC=C135509 TESTCD=C25334 | HCG (Serum HCG Measurement): BC=C73495 TESTCD=C64851</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>QC-15</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder BC_IDs (NCIt code pending)</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>NEW_LZZT (TTS Acceptability Survey) | NEW_LZZT4 (TTS Acceptability Survey -  Pa) | NEW_LZZT1 (TTS Acceptability Survey -  Pa) | NEW_LZZT3 (TTS Acceptability Survey -  Pa) | NEW_LZZT2 (TTS Acceptability Survey -  Pa) | NEW_1 (Urine Glucose Test Strip Measu)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>QC-13</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>BC_Synonyms: preferred term not stripped</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>C100106 (ADAS-Cog CDISC Version Functio) | C211913 (CDISC QRS Instruments Question) | C91102 (Clinical or Research Assessmen) | C101875 (EQ-5D-5L Questionnaire Questio) | C48227 (Lost To Follow-Up)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>QC-14</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>TESTCD_NCIt differs from NCIt_Code</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>HEIGHT (Body Height): BC=C164634 TESTCD=C25347 | WEIGHT (Body Weight): BC=C81328 TESTCD=C25208 | INTP (Electrocardiogram Analysis): BC=C181655 TESTCD=C41255 | GLUCPE (Glucose Measurement): BC=C105585 TESTCD=C163446 | MICROCY (Microcyte to Erythrocyte Ratio): BC=C201227 TESTCD=C64822 | LENGTH (Organ Craniocaudal Length Meas): BC=C135509 TESTCD=C25334 | HCG (Serum HCG Measurement): BC=C73495 TESTCD=C64851</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>QC-15</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>BC_Scope=Study: trial-level metadata included as BCs</t>
         </is>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" s="10" t="n">
         <v>193</v>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>192 BCs, 129 DSS rows, 63 hierarchy rows | Domains: TS</t>
         </is>

--- a/cosmos-bc-dss/reports/COSMoS_BC_DSS_QC.xlsx
+++ b/cosmos-bc-dss/reports/COSMoS_BC_DSS_QC.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,21 +36,17 @@
       <b val="1"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="00276221"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="009C6500"/>
     </font>
     <font>
-      <color rgb="00276221"/>
-    </font>
-    <font>
       <color rgb="007B6000"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -71,20 +67,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
         <bgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -120,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -147,12 +137,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -577,7 +561,7 @@
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-09</t>
+          <t>Generated: 2026-04-16</t>
         </is>
       </c>
     </row>
@@ -792,7 +776,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -801,13 +785,9 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>C113243 (2 usages) | C449 (26 usages) | C812 (7 usages) | C95940 (3 usages)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -826,84 +806,80 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>AUTOPSY (1 usages) | C179788 (1 usages) | PINCH DYNAMOMETRY (1 usages)</t>
+          <t>AUTOPSY (1 usages) | PINCH DYNAMOMETRY (1 usages)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>QC-03</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>CT unmapped: Unit</t>
         </is>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="8" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>QC-04</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>DSS rows with no TESTCD (no CT test code in COSMoS source)</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="8" t="n">
         <v>48</v>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>ADVEVENT (DS) | ARIGEABCH (IS) | ARIGEABFP (IS) | ARIGEABM (IS) | ARIGEABMR (IS) | ARIGEABPC (IS) | BRTHDTC (DM) | PROTCOMP (DS) | CTSCAN (PR) | CTSCANCHEST (PR)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>QC-05</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Specimen present but Specimen_NCIt blank</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>C449 | C812 | C113243 | C95940</t>
-        </is>
-      </c>
+      <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -956,50 +932,50 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>QC-08</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Multi-result DSS (same TESTCD+Domain+Specimen)</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>IS ARIGEAB (SERUM; SERUM OR PLASMA; BLOOD) x87 | IS MBIGGAB (SERUM; SERUM OR PLASMA; BLOOD) x63 | IS ARIGGAB (SERUM; SERUM OR PLASMA; BLOOD) x53 | IS MBIMAB (SERUM; SERUM OR PLASMA; BLOOD) x52 | IS ARIGAAB (SERUM; SERUM OR PLASMA; BLOOD) x17 | IS ATIGMAB (SERUM; SERUM OR PLASMA; BLOOD) x12 | GF SEQREAR (C449) x6 | GF SNV (C449) x6 | GF SHRTVAR (C449) x5 | GF TRNSCPTN (C812) x5</t>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>IS ARIGEAB (SERUM; SERUM OR PLASMA; BLOOD) x87 | IS MBIGGAB (SERUM; SERUM OR PLASMA; BLOOD) x63 | IS ARIGGAB (SERUM; SERUM OR PLASMA; BLOOD) x53 | IS MBIMAB (SERUM; SERUM OR PLASMA; BLOOD) x52 | IS ARIGAAB (SERUM; SERUM OR PLASMA; BLOOD) x17 | IS ATIGMAB (SERUM; SERUM OR PLASMA; BLOOD) x12 | GF SEQREAR (DNA) x6 | GF SNV (DNA) x6 | GF SHRTVAR (DNA) x5 | GF TRNSCPTN (RNA) x5</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>QC-09</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>BC_only_no_DS (192 BCs) -- top categories</t>
         </is>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="8" t="n">
         <v>192</v>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>QRS: 119 | Functional Assessment: 96 | ADAS-Cog: 95 | ADC: 95 | Alzheimer's Disease Assessment Scale-Cognitive CDISC Version Functional Test: 95 | ADAS-Cog CDISC Version Functional Test Question: 94 | Laboratory Tests: 16 | Clinical or Research Assessment Classification: 14 | Gene Expression Analysis: 11 | Genetic Testing: 10</t>
         </is>
@@ -1081,46 +1057,46 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>QC-11c</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Result_Scale: no unexpected values</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="8" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>QC-12</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Placeholder BC_IDs (NCIt code pending)</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>NEW_LZZT (TTS Acceptability Survey) | NEW_LZZT4 (TTS Acceptability Survey -  Pa) | NEW_LZZT1 (TTS Acceptability Survey -  Pa) | NEW_LZZT3 (TTS Acceptability Survey -  Pa) | NEW_LZZT2 (TTS Acceptability Survey -  Pa) | NEW_1 (Urine Glucose Test Strip Measu)</t>
         </is>
@@ -1152,50 +1128,50 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>QC-14</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>TESTCD_NCIt differs from NCIt_Code</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>HEIGHT (Body Height): BC=C164634 TESTCD=C25347 | WEIGHT (Body Weight): BC=C81328 TESTCD=C25208 | INTP (Electrocardiogram Analysis): BC=C181655 TESTCD=C41255 | GLUCPE (Glucose Measurement): BC=C105585 TESTCD=C163446 | MICROCY (Microcyte to Erythrocyte Ratio): BC=C201227 TESTCD=C64822 | LENGTH (Organ Craniocaudal Length Meas): BC=C135509 TESTCD=C25334 | HCG (Serum HCG Measurement): BC=C73495 TESTCD=C64851</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>QC-15</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>BC_Scope=Study: trial-level metadata included as BCs</t>
         </is>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="8" t="n">
         <v>193</v>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>192 BCs, 129 DSS rows, 63 hierarchy rows | Domains: TS</t>
         </is>
